--- a/OCT_2026/Reports/Purchase order Distributor.xlsx
+++ b/OCT_2026/Reports/Purchase order Distributor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A107569A-BFE9-4DD6-AD84-FE1FE03402DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F432DECB-3F94-4528-9EE7-C3072C7F481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="64">
   <si>
     <t>SKU Description</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Ayyan Gujrat</t>
+  </si>
+  <si>
+    <t>Indomie Chicken ( R ) 4 in 1</t>
   </si>
 </sst>
 </file>
@@ -5349,7 +5352,7 @@
       <selection activeCell="E8" sqref="E8"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-      <autoFilter ref="A2:H123" xr:uid="{6FCB1E25-E88B-427F-840C-D79515B07077}"/>
+      <autoFilter ref="A2:H123" xr:uid="{74C524F9-A8F9-471C-BE93-24F31D607649}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="15">
@@ -5410,7 +5413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="12.1796875" hidden="1" customWidth="1"/>
@@ -5430,8 +5433,8 @@
     <col min="15" max="15" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="2" spans="1:17" ht="46.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="2" spans="1:15" ht="46.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="148" t="s">
         <v>26</v>
       </c>
@@ -5449,7 +5452,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:15" ht="28.5" x14ac:dyDescent="0.5">
       <c r="B3" s="151"/>
       <c r="C3" s="166" t="s">
         <v>25</v>
@@ -5466,10 +5469,10 @@
       </c>
       <c r="L3" s="125">
         <f>SUM(J13:J22)</f>
-        <v>2092035.5999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
+        <v>1765152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.5">
       <c r="B4" s="152"/>
       <c r="C4" s="168" t="s">
         <v>1</v>
@@ -5477,7 +5480,7 @@
       <c r="D4" s="169"/>
       <c r="E4" s="158">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46311</v>
       </c>
       <c r="F4" s="159"/>
       <c r="G4" s="160"/>
@@ -5487,10 +5490,10 @@
       </c>
       <c r="L4" s="125">
         <f>SUM(L13:L19)</f>
-        <v>488135.59322033892</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="28.5" x14ac:dyDescent="0.5">
       <c r="B5" s="152"/>
       <c r="C5" s="168" t="s">
         <v>24</v>
@@ -5498,7 +5501,7 @@
       <c r="D5" s="169"/>
       <c r="E5" s="158">
         <f ca="1">+E4+1</f>
-        <v>46294</v>
+        <v>46312</v>
       </c>
       <c r="F5" s="159"/>
       <c r="G5" s="160"/>
@@ -5508,10 +5511,10 @@
       </c>
       <c r="L5" s="125">
         <f>L4+L3</f>
-        <v>2580171.1932203388</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+        <v>1765152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="153"/>
       <c r="C6" s="170" t="s">
         <v>2</v>
@@ -5528,10 +5531,10 @@
       </c>
       <c r="L6" s="126">
         <f>L5*0.1%</f>
-        <v>2580.1711932203389</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="23.5" hidden="1" x14ac:dyDescent="0.5">
+        <v>1765.152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="23.5" hidden="1" x14ac:dyDescent="0.5">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -5545,7 +5548,7 @@
       <c r="L7" s="125"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:17" ht="23.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:15" ht="23.5" x14ac:dyDescent="0.5">
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -5555,11 +5558,11 @@
       <c r="K8" s="1"/>
       <c r="L8" s="125">
         <f>+L5+L6</f>
-        <v>2582751.364413559</v>
+        <v>1766917.152</v>
       </c>
       <c r="N8" s="115"/>
     </row>
-    <row r="9" spans="1:17" ht="23.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:15" ht="23.5" x14ac:dyDescent="0.5">
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -5569,11 +5572,11 @@
       <c r="K9" s="1"/>
       <c r="L9" s="130">
         <f>L8*J9</f>
-        <v>1549650.8186481353</v>
+        <v>1060150.2911999999</v>
       </c>
       <c r="N9" s="115"/>
     </row>
-    <row r="10" spans="1:17" ht="23.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:15" ht="23.5" x14ac:dyDescent="0.5">
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -5583,16 +5586,16 @@
       <c r="K10" s="1"/>
       <c r="L10" s="130">
         <f>L8*J10</f>
-        <v>1033100.5457654237</v>
+        <v>706766.86080000002</v>
       </c>
       <c r="N10" s="115"/>
     </row>
-    <row r="11" spans="1:17" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="H11" s="1"/>
       <c r="J11" s="7"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:17" ht="56" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" ht="56" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="72" t="s">
         <v>31</v>
       </c>
@@ -5626,7 +5629,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A13" s="113"/>
       <c r="B13" s="111" t="s">
         <v>45</v>
@@ -5651,34 +5654,21 @@
         <f>VLOOKUP($B13,'SKU Details'!D6:Y58,17,0)</f>
         <v>1699.7849999999999</v>
       </c>
-      <c r="H13" s="103">
-        <v>100</v>
-      </c>
+      <c r="H13" s="103"/>
       <c r="I13" s="81"/>
       <c r="J13" s="82">
         <f t="shared" ref="J13:J21" si="0">(H13*G13)</f>
-        <v>169978.5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="91"/>
       <c r="L13" s="88">
         <f>+P13</f>
-        <v>39661.016949152523</v>
+        <v>0</v>
       </c>
       <c r="N13" s="127"/>
-      <c r="O13" s="128">
-        <f>+F13-F13/1.18</f>
-        <v>9.9152542372881314</v>
-      </c>
-      <c r="P13">
-        <f>+O13*Q13</f>
-        <v>39661.016949152523</v>
-      </c>
-      <c r="Q13">
-        <f>+E13*H13</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="O13" s="128"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A14" s="114"/>
       <c r="B14" s="112" t="s">
         <v>44</v>
@@ -5703,34 +5693,21 @@
         <f>VLOOKUP($B14,'SKU Details'!D7:Y59,17,0)</f>
         <v>1699.7849999999999</v>
       </c>
-      <c r="H14" s="97">
-        <v>100</v>
-      </c>
+      <c r="H14" s="97"/>
       <c r="I14" s="83"/>
       <c r="J14" s="16">
         <f t="shared" si="0"/>
-        <v>169978.5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="92"/>
       <c r="L14" s="89">
         <f>+P14</f>
-        <v>39661.016949152523</v>
+        <v>0</v>
       </c>
       <c r="N14" s="127"/>
-      <c r="O14" s="128">
-        <f t="shared" ref="O14:O19" si="1">+F14-F14/1.18</f>
-        <v>9.9152542372881314</v>
-      </c>
-      <c r="P14">
-        <f>+O14*Q14</f>
-        <v>39661.016949152523</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" ref="Q14:Q18" si="2">+E14*H14</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="O14" s="128"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A15" s="114"/>
       <c r="B15" s="112" t="s">
         <v>43</v>
@@ -5755,34 +5732,21 @@
         <f>VLOOKUP($B15,'SKU Details'!D8:Y60,17,0)</f>
         <v>1699.7849999999999</v>
       </c>
-      <c r="H15" s="97">
-        <v>200</v>
-      </c>
+      <c r="H15" s="97"/>
       <c r="I15" s="83"/>
       <c r="J15" s="16">
         <f t="shared" si="0"/>
-        <v>339957</v>
+        <v>0</v>
       </c>
       <c r="K15" s="92"/>
       <c r="L15" s="89">
         <f>+P15</f>
-        <v>79322.033898305046</v>
+        <v>0</v>
       </c>
       <c r="N15" s="127"/>
-      <c r="O15" s="128">
-        <f t="shared" si="1"/>
-        <v>9.9152542372881314</v>
-      </c>
-      <c r="P15">
-        <f>+O15*Q15</f>
-        <v>79322.033898305046</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="2"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="O15" s="128"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A16" s="114"/>
       <c r="B16" s="112" t="s">
         <v>48</v>
@@ -5808,33 +5772,22 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H16" s="97">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="I16" s="83"/>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>353030.40000000002</v>
+        <v>588384</v>
       </c>
       <c r="K16" s="92"/>
       <c r="L16" s="89">
-        <f t="shared" ref="L16:L19" si="3">+P16</f>
-        <v>82372.881355932201</v>
+        <f t="shared" ref="L16:L19" si="1">+P16</f>
+        <v>0</v>
       </c>
       <c r="N16" s="127"/>
-      <c r="O16" s="128">
-        <f t="shared" si="1"/>
-        <v>13.728813559322035</v>
-      </c>
-      <c r="P16">
-        <f>+O16*Q16</f>
-        <v>82372.881355932201</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="2"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="O16" s="128"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A17" s="114"/>
       <c r="B17" s="112" t="s">
         <v>47</v>
@@ -5860,33 +5813,22 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H17" s="97">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I17" s="83"/>
       <c r="J17" s="16">
         <f t="shared" si="0"/>
-        <v>588384</v>
+        <v>353030.40000000002</v>
       </c>
       <c r="K17" s="92"/>
       <c r="L17" s="89">
-        <f t="shared" si="3"/>
-        <v>137288.13559322036</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="N17" s="127"/>
-      <c r="O17" s="128">
-        <f t="shared" si="1"/>
-        <v>13.728813559322035</v>
-      </c>
-      <c r="P17">
-        <f>+O17*Q17</f>
-        <v>137288.13559322036</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="2"/>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="O17" s="128"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A18" s="114"/>
       <c r="B18" s="112" t="s">
         <v>46</v>
@@ -5912,33 +5854,22 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H18" s="97">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="I18" s="83"/>
       <c r="J18" s="16">
         <f t="shared" si="0"/>
-        <v>470707.20000000001</v>
+        <v>823737.6</v>
       </c>
       <c r="K18" s="92"/>
       <c r="L18" s="89">
-        <f t="shared" si="3"/>
-        <v>109830.50847457627</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="N18" s="127"/>
-      <c r="O18" s="128">
-        <f t="shared" si="1"/>
-        <v>13.728813559322035</v>
-      </c>
-      <c r="P18">
-        <f t="shared" ref="P18" si="4">+O18*Q18</f>
-        <v>109830.50847457627</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="2"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="O18" s="128"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A19" s="114"/>
       <c r="B19" s="112" t="s">
         <v>50</v>
@@ -5971,24 +5902,13 @@
       </c>
       <c r="K19" s="93"/>
       <c r="L19" s="89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N19" s="127"/>
-      <c r="O19" s="128">
-        <f t="shared" si="1"/>
-        <v>7.6271186440677923</v>
-      </c>
-      <c r="P19">
-        <f>+O19*Q19</f>
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <f>+E19*H19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.5">
+      <c r="O19" s="128"/>
+    </row>
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.5">
       <c r="A20" s="114"/>
       <c r="B20" s="112" t="s">
         <v>51</v>
@@ -6025,7 +5945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.5">
       <c r="A21" s="114"/>
       <c r="B21" s="112" t="s">
         <v>52</v>
@@ -6062,27 +5982,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="114"/>
       <c r="B22" s="112"/>
-      <c r="C22" s="14"/>
+      <c r="C22" s="14" t="s">
+        <v>63</v>
+      </c>
       <c r="D22" s="14"/>
-      <c r="E22" s="84" t="str">
-        <f>IFERROR(VLOOKUP(B22,'SKU Details'!A:F,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="84"/>
-      <c r="G22" s="15" t="str">
-        <f>IFERROR(VLOOKUP(B22,'SKU Details'!A:F,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="18"/>
+      <c r="E22" s="84">
+        <v>40</v>
+      </c>
+      <c r="F22" s="12">
+        <v>170</v>
+      </c>
+      <c r="G22" s="102" t="e">
+        <f>VLOOKUP($B22,'SKU Details'!D15:Y67,17,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H22" s="18">
+        <v>250</v>
+      </c>
       <c r="I22" s="85"/>
       <c r="J22" s="13"/>
       <c r="K22" s="95"/>
       <c r="L22" s="90"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.5">
       <c r="C23" s="2"/>
       <c r="D23" s="117"/>
       <c r="E23" s="5"/>
@@ -6135,7 +6060,7 @@
     <cfRule type="duplicateValues" dxfId="17" priority="23"/>
     <cfRule type="duplicateValues" dxfId="16" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13:B22 G22:H22">
+  <conditionalFormatting sqref="A13:B22 H22">
     <cfRule type="cellIs" dxfId="15" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
@@ -6164,7 +6089,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Order No " prompt="_x000a_Example,_x000a__x000a_alphabates-Year-Month-order serial No_x000a__x000a_AB-2019-May-01" sqref="E6:H6" xr:uid="{00000000-0002-0000-0100-000000000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Distributor Name " prompt="_x000a_Example,_x000a__x000a_ABC-Distributor" sqref="E3:H3" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date Error" error="Please type in the format_x000a__x000a_01-01-2019" prompt="Please type in the format_x000a__x000a_01-01-2019" sqref="E4:H5" xr:uid="{00000000-0002-0000-0100-000002000000}">

--- a/OCT_2026/Reports/Purchase order Distributor.xlsx
+++ b/OCT_2026/Reports/Purchase order Distributor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F432DECB-3F94-4528-9EE7-C3072C7F481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB25B76-4F42-4EC1-AF23-0D9BE8C540C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
   <si>
     <t>SKU Description</t>
   </si>
@@ -223,6 +223,15 @@
   <si>
     <t>Indomie Chicken ( R ) 4 in 1</t>
   </si>
+  <si>
+    <t>CCN PROMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN PROMO </t>
+  </si>
+  <si>
+    <t>Indomie Chicken ® 4 in 1</t>
+  </si>
 </sst>
 </file>
 
@@ -238,7 +247,7 @@
     <numFmt numFmtId="169" formatCode="0.0000000000000"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="43" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -548,6 +557,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -1523,7 +1540,7 @@
     <xf numFmtId="9" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1871,6 +1888,36 @@
     <xf numFmtId="1" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="21" borderId="1" xfId="114" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="39" fillId="21" borderId="1" xfId="114" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="39" fillId="21" borderId="1" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="39" fillId="21" borderId="1" xfId="114" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="39" fillId="21" borderId="1" xfId="113" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="39" fillId="21" borderId="1" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2003,6 +2050,7 @@
     <xf numFmtId="3" fontId="18" fillId="3" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="115">
     <cellStyle name="Comma" xfId="17" builtinId="3"/>
@@ -2121,7 +2169,7 @@
     <cellStyle name="Yellow" xfId="18" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
     <cellStyle name="Yellow 2" xfId="30" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="24">
     <dxf>
       <font>
         <b/>
@@ -2244,15 +2292,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2662,12 +2701,13 @@
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.1796875" style="107" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="4.81640625" style="107" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="107" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="107" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.81640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.81640625" style="21" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="3.453125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
@@ -2694,97 +2734,97 @@
       </c>
     </row>
     <row r="3" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="132"/>
-      <c r="B3" s="132"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="N3" s="133"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="133"/>
-      <c r="R3" s="133"/>
-      <c r="S3" s="133"/>
-      <c r="T3" s="133"/>
-      <c r="U3" s="133"/>
-      <c r="V3" s="133"/>
-      <c r="W3" s="133"/>
-      <c r="X3" s="133"/>
-      <c r="Y3" s="133"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="142"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="143"/>
+      <c r="R3" s="143"/>
+      <c r="S3" s="143"/>
+      <c r="T3" s="143"/>
+      <c r="U3" s="143"/>
+      <c r="V3" s="143"/>
+      <c r="W3" s="143"/>
+      <c r="X3" s="143"/>
+      <c r="Y3" s="143"/>
     </row>
     <row r="4" spans="1:29" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="134" t="s">
+      <c r="A4" s="144" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="120" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="120"/>
-      <c r="D4" s="146" t="s">
+      <c r="D4" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="136" t="s">
+      <c r="E4" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="138" t="s">
+      <c r="F4" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="138"/>
-      <c r="H4" s="139" t="s">
+      <c r="G4" s="148"/>
+      <c r="H4" s="149" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="139"/>
-      <c r="J4" s="140" t="s">
+      <c r="I4" s="149"/>
+      <c r="J4" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="141"/>
-      <c r="L4" s="140" t="s">
+      <c r="K4" s="151"/>
+      <c r="L4" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="141"/>
-      <c r="N4" s="142" t="s">
+      <c r="M4" s="151"/>
+      <c r="N4" s="152" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="142"/>
-      <c r="P4" s="140" t="s">
+      <c r="O4" s="152"/>
+      <c r="P4" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="141"/>
-      <c r="R4" s="140" t="s">
+      <c r="Q4" s="151"/>
+      <c r="R4" s="150" t="s">
         <v>41</v>
       </c>
-      <c r="S4" s="141"/>
-      <c r="T4" s="143" t="s">
+      <c r="S4" s="151"/>
+      <c r="T4" s="153" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="143"/>
-      <c r="V4" s="144" t="s">
+      <c r="U4" s="153"/>
+      <c r="V4" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="W4" s="145"/>
-      <c r="X4" s="144" t="s">
+      <c r="W4" s="155"/>
+      <c r="X4" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="Y4" s="145"/>
+      <c r="Y4" s="155"/>
     </row>
     <row r="5" spans="1:29" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="135"/>
+      <c r="A5" s="145"/>
       <c r="B5" s="108" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="108" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="147"/>
-      <c r="E5" s="137"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="147"/>
       <c r="F5" s="23" t="s">
         <v>18</v>
       </c>
@@ -2933,7 +2973,7 @@
         <v>50.143657499999996</v>
       </c>
       <c r="AA6" s="37">
-        <f t="shared" ref="AA6:AA14" si="2">(F6*G6)/1000</f>
+        <f t="shared" ref="AA6:AA15" si="2">(F6*G6)/1000</f>
         <v>2.8</v>
       </c>
       <c r="AC6" s="41"/>
@@ -2978,7 +3018,7 @@
         <v>2098.5</v>
       </c>
       <c r="M7" s="37">
-        <f t="shared" ref="M7:M14" si="5">L7/G7</f>
+        <f t="shared" ref="M7:M15" si="5">L7/G7</f>
         <v>52.462499999999999</v>
       </c>
       <c r="N7" s="121">
@@ -3151,7 +3191,7 @@
         <v>3544.8320000000003</v>
       </c>
       <c r="K9" s="36">
-        <f t="shared" ref="K9:K14" si="16">M9*1.22</f>
+        <f t="shared" ref="K9:K15" si="16">M9*1.22</f>
         <v>88.620800000000003</v>
       </c>
       <c r="L9" s="37">
@@ -3596,7 +3636,7 @@
         <v>50</v>
       </c>
       <c r="J14" s="36">
-        <f t="shared" ref="J14" si="29">K14*G14</f>
+        <f t="shared" ref="J14:J15" si="29">K14*G14</f>
         <v>1914.4240000000002</v>
       </c>
       <c r="K14" s="36">
@@ -3620,12 +3660,12 @@
       </c>
       <c r="P14" s="38"/>
       <c r="Q14" s="39">
-        <f t="shared" ref="Q14" si="31">P14*M14</f>
+        <f t="shared" ref="Q14:Q15" si="31">P14*M14</f>
         <v>0</v>
       </c>
       <c r="R14" s="40"/>
       <c r="S14" s="39">
-        <f t="shared" ref="S14" si="32">R14*M14</f>
+        <f t="shared" ref="S14:S15" si="32">R14*M14</f>
         <v>0</v>
       </c>
       <c r="T14" s="37">
@@ -3663,30 +3703,87 @@
         <v>10</v>
       </c>
       <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
-      <c r="V15" s="66"/>
-      <c r="W15" s="66"/>
-      <c r="X15" s="66"/>
-      <c r="Y15" s="66"/>
-      <c r="AA15" s="66"/>
+      <c r="C15" s="132" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="132" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="133" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="134">
+        <v>70</v>
+      </c>
+      <c r="G15" s="135">
+        <v>48</v>
+      </c>
+      <c r="H15" s="135">
+        <v>2400</v>
+      </c>
+      <c r="I15" s="136">
+        <v>190</v>
+      </c>
+      <c r="J15" s="136">
+        <f t="shared" si="29"/>
+        <v>2788.5662000000002</v>
+      </c>
+      <c r="K15" s="136">
+        <f t="shared" si="16"/>
+        <v>58.095129166666666</v>
+      </c>
+      <c r="L15" s="137">
+        <v>2285.71</v>
+      </c>
+      <c r="M15" s="137">
+        <f t="shared" si="5"/>
+        <v>47.618958333333332</v>
+      </c>
+      <c r="N15" s="138">
+        <v>0.19</v>
+      </c>
+      <c r="O15" s="139">
+        <f>N15*M15</f>
+        <v>9.0476020833333326</v>
+      </c>
+      <c r="P15" s="140"/>
+      <c r="Q15" s="139">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="141"/>
+      <c r="S15" s="139">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="137">
+        <f t="shared" ref="T15" si="40">U15*G15</f>
+        <v>1851.4250999999999</v>
+      </c>
+      <c r="U15" s="137">
+        <f t="shared" ref="U15" si="41">M15-O15-Q15-S15</f>
+        <v>38.571356250000001</v>
+      </c>
+      <c r="V15" s="137">
+        <f t="shared" ref="V15" si="42">T15*$V$2</f>
+        <v>333.25651799999997</v>
+      </c>
+      <c r="W15" s="137">
+        <f t="shared" ref="W15" si="43">U15*$V$2</f>
+        <v>6.9428441249999997</v>
+      </c>
+      <c r="X15" s="137">
+        <f t="shared" ref="X15" si="44">T15+V15</f>
+        <v>2184.6816180000001</v>
+      </c>
+      <c r="Y15" s="137">
+        <f t="shared" ref="Y15" si="45">U15+W15</f>
+        <v>45.514200375000001</v>
+      </c>
+      <c r="AA15" s="66">
+        <f t="shared" si="2"/>
+        <v>3.36</v>
+      </c>
     </row>
     <row r="16" spans="1:29" s="70" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A16" s="61">
@@ -4880,7 +4977,7 @@
     </row>
     <row r="55" spans="1:27" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A55" s="32">
-        <f t="shared" ref="A55:A58" si="40">+A54+1</f>
+        <f t="shared" ref="A55:A58" si="46">+A54+1</f>
         <v>45</v>
       </c>
       <c r="B55" s="106"/>
@@ -4911,7 +5008,7 @@
     </row>
     <row r="56" spans="1:27" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A56" s="32">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>46</v>
       </c>
       <c r="B56" s="106"/>
@@ -4942,7 +5039,7 @@
     </row>
     <row r="57" spans="1:27" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A57" s="32">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>47</v>
       </c>
       <c r="B57" s="106"/>
@@ -4973,7 +5070,7 @@
     </row>
     <row r="58" spans="1:27" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A58" s="32">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>48</v>
       </c>
       <c r="B58" s="106"/>
@@ -5090,7 +5187,7 @@
     </row>
     <row r="62" spans="1:27" s="86" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A62" s="32">
-        <f t="shared" ref="A62:A66" si="41">+A61+1</f>
+        <f t="shared" ref="A62:A66" si="47">+A61+1</f>
         <v>51</v>
       </c>
       <c r="B62" s="106"/>
@@ -5122,7 +5219,7 @@
     </row>
     <row r="63" spans="1:27" s="86" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A63" s="32">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>52</v>
       </c>
       <c r="B63" s="106"/>
@@ -5154,7 +5251,7 @@
     </row>
     <row r="64" spans="1:27" s="86" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A64" s="32">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>53</v>
       </c>
       <c r="B64" s="106"/>
@@ -5186,7 +5283,7 @@
     </row>
     <row r="65" spans="1:27" s="86" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A65" s="32">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>54</v>
       </c>
       <c r="B65" s="106"/>
@@ -5218,7 +5315,7 @@
     </row>
     <row r="66" spans="1:27" s="86" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A66" s="32">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>55</v>
       </c>
       <c r="B66" s="106"/>
@@ -5283,7 +5380,7 @@
     </row>
     <row r="69" spans="1:27" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A69" s="32">
-        <f t="shared" ref="A69:A70" si="42">+A68+1</f>
+        <f t="shared" ref="A69:A70" si="48">+A68+1</f>
         <v>57</v>
       </c>
       <c r="B69" s="118"/>
@@ -5314,7 +5411,7 @@
     </row>
     <row r="70" spans="1:27" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A70" s="32">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>58</v>
       </c>
       <c r="B70" s="118"/>
@@ -5352,7 +5449,7 @@
       <selection activeCell="E8" sqref="E8"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-      <autoFilter ref="A2:H123" xr:uid="{74C524F9-A8F9-471C-BE93-24F31D607649}"/>
+      <autoFilter ref="A2:H123" xr:uid="{0DB22CB4-1492-4A33-9B20-2457272F2CCB}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="15">
@@ -5373,35 +5470,35 @@
     <mergeCell ref="D4:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:D3 A71:D145 D4 A4:A5 B5:C5">
-    <cfRule type="cellIs" dxfId="24" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:D67">
-    <cfRule type="cellIs" dxfId="23" priority="8" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A68:D70">
-    <cfRule type="cellIs" dxfId="22" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A159:D163">
-    <cfRule type="cellIs" dxfId="21" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A170:D172">
-    <cfRule type="cellIs" dxfId="20" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D3 D71:D1048576 D6:D67">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:D66">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -5413,13 +5510,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="12.1796875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" style="116" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" style="116" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
@@ -5433,58 +5530,58 @@
     <col min="15" max="15" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="2" spans="1:15" ht="46.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="148" t="s">
+    <row r="1" spans="1:16" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="2" spans="1:16" ht="46.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="150"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="160"/>
       <c r="J2" s="122" t="s">
         <v>6</v>
       </c>
       <c r="L2" s="124">
         <f>SUM(H13:H22)</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B3" s="151"/>
-      <c r="C3" s="166" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="28.5" x14ac:dyDescent="0.5">
+      <c r="B3" s="161"/>
+      <c r="C3" s="176" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="154" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="155"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="157"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="167"/>
       <c r="J3" s="123" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="125">
         <f>SUM(J13:J22)</f>
-        <v>1765152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B4" s="152"/>
-      <c r="C4" s="168" t="s">
+        <v>2060724.5153999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="28.5" x14ac:dyDescent="0.5">
+      <c r="B4" s="162"/>
+      <c r="C4" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="169"/>
-      <c r="E4" s="158">
+      <c r="D4" s="179"/>
+      <c r="E4" s="168">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
-      </c>
-      <c r="F4" s="159"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="161"/>
+        <v>46322</v>
+      </c>
+      <c r="F4" s="169"/>
+      <c r="G4" s="170"/>
+      <c r="H4" s="171"/>
       <c r="J4" s="123" t="s">
         <v>54</v>
       </c>
@@ -5492,49 +5589,50 @@
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B5" s="152"/>
-      <c r="C5" s="168" t="s">
+      <c r="P4" s="182"/>
+    </row>
+    <row r="5" spans="1:16" ht="28.5" x14ac:dyDescent="0.5">
+      <c r="B5" s="162"/>
+      <c r="C5" s="178" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="169"/>
-      <c r="E5" s="158">
+      <c r="D5" s="179"/>
+      <c r="E5" s="168">
         <f ca="1">+E4+1</f>
-        <v>46312</v>
-      </c>
-      <c r="F5" s="159"/>
-      <c r="G5" s="160"/>
-      <c r="H5" s="161"/>
+        <v>46323</v>
+      </c>
+      <c r="F5" s="169"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="171"/>
       <c r="J5" s="123" t="s">
         <v>4</v>
       </c>
       <c r="L5" s="125">
         <f>L4+L3</f>
-        <v>1765152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="153"/>
-      <c r="C6" s="170" t="s">
+        <v>2060724.5153999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="163"/>
+      <c r="C6" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="171"/>
-      <c r="E6" s="162" t="s">
+      <c r="D6" s="181"/>
+      <c r="E6" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="163"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="165"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="175"/>
       <c r="J6" s="123" t="s">
         <v>55</v>
       </c>
       <c r="L6" s="126">
         <f>L5*0.1%</f>
-        <v>1765.152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="23.5" hidden="1" x14ac:dyDescent="0.5">
+        <v>2060.7245153999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.5" hidden="1" x14ac:dyDescent="0.5">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -5548,7 +5646,7 @@
       <c r="L7" s="125"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="23.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:16" ht="23.5" x14ac:dyDescent="0.5">
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -5558,11 +5656,11 @@
       <c r="K8" s="1"/>
       <c r="L8" s="125">
         <f>+L5+L6</f>
-        <v>1766917.152</v>
+        <v>2062785.2399153998</v>
       </c>
       <c r="N8" s="115"/>
     </row>
-    <row r="9" spans="1:15" ht="23.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:16" ht="23.5" x14ac:dyDescent="0.5">
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -5572,11 +5670,11 @@
       <c r="K9" s="1"/>
       <c r="L9" s="130">
         <f>L8*J9</f>
-        <v>1060150.2911999999</v>
+        <v>1237671.1439492397</v>
       </c>
       <c r="N9" s="115"/>
     </row>
-    <row r="10" spans="1:15" ht="23.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:16" ht="23.5" x14ac:dyDescent="0.5">
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -5586,16 +5684,16 @@
       <c r="K10" s="1"/>
       <c r="L10" s="130">
         <f>L8*J10</f>
-        <v>706766.86080000002</v>
+        <v>825114.09596615995</v>
       </c>
       <c r="N10" s="115"/>
     </row>
-    <row r="11" spans="1:15" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="H11" s="1"/>
       <c r="J11" s="7"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:15" ht="56" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" ht="56" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="72" t="s">
         <v>31</v>
       </c>
@@ -5629,7 +5727,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A13" s="113"/>
       <c r="B13" s="111" t="s">
         <v>45</v>
@@ -5654,11 +5752,13 @@
         <f>VLOOKUP($B13,'SKU Details'!D6:Y58,17,0)</f>
         <v>1699.7849999999999</v>
       </c>
-      <c r="H13" s="103"/>
+      <c r="H13" s="103">
+        <v>250</v>
+      </c>
       <c r="I13" s="81"/>
       <c r="J13" s="82">
-        <f t="shared" ref="J13:J21" si="0">(H13*G13)</f>
-        <v>0</v>
+        <f t="shared" ref="J13:J22" si="0">(H13*G13)</f>
+        <v>424946.24999999994</v>
       </c>
       <c r="K13" s="91"/>
       <c r="L13" s="88">
@@ -5668,7 +5768,7 @@
       <c r="N13" s="127"/>
       <c r="O13" s="128"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A14" s="114"/>
       <c r="B14" s="112" t="s">
         <v>44</v>
@@ -5693,11 +5793,13 @@
         <f>VLOOKUP($B14,'SKU Details'!D7:Y59,17,0)</f>
         <v>1699.7849999999999</v>
       </c>
-      <c r="H14" s="97"/>
+      <c r="H14" s="97">
+        <v>250</v>
+      </c>
       <c r="I14" s="83"/>
       <c r="J14" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>424946.24999999994</v>
       </c>
       <c r="K14" s="92"/>
       <c r="L14" s="89">
@@ -5707,7 +5809,7 @@
       <c r="N14" s="127"/>
       <c r="O14" s="128"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A15" s="114"/>
       <c r="B15" s="112" t="s">
         <v>43</v>
@@ -5746,7 +5848,7 @@
       <c r="N15" s="127"/>
       <c r="O15" s="128"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A16" s="114"/>
       <c r="B16" s="112" t="s">
         <v>48</v>
@@ -5771,13 +5873,11 @@
         <f>VLOOKUP($B16,'SKU Details'!D9:Y61,17,0)</f>
         <v>2353.5360000000001</v>
       </c>
-      <c r="H16" s="97">
-        <v>250</v>
-      </c>
+      <c r="H16" s="97"/>
       <c r="I16" s="83"/>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>588384</v>
+        <v>0</v>
       </c>
       <c r="K16" s="92"/>
       <c r="L16" s="89">
@@ -5812,13 +5912,11 @@
         <f>VLOOKUP($B17,'SKU Details'!D10:Y62,17,0)</f>
         <v>2353.5360000000001</v>
       </c>
-      <c r="H17" s="97">
-        <v>150</v>
-      </c>
+      <c r="H17" s="97"/>
       <c r="I17" s="83"/>
       <c r="J17" s="16">
         <f t="shared" si="0"/>
-        <v>353030.40000000002</v>
+        <v>0</v>
       </c>
       <c r="K17" s="92"/>
       <c r="L17" s="89">
@@ -5853,13 +5951,11 @@
         <f>VLOOKUP($B18,'SKU Details'!D11:Y63,17,0)</f>
         <v>2353.5360000000001</v>
       </c>
-      <c r="H18" s="97">
-        <v>350</v>
-      </c>
+      <c r="H18" s="97"/>
       <c r="I18" s="83"/>
       <c r="J18" s="16">
         <f t="shared" si="0"/>
-        <v>823737.6</v>
+        <v>0</v>
       </c>
       <c r="K18" s="92"/>
       <c r="L18" s="89">
@@ -5869,7 +5965,7 @@
       <c r="N18" s="127"/>
       <c r="O18" s="128"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.5">
       <c r="A19" s="114"/>
       <c r="B19" s="112" t="s">
         <v>50</v>
@@ -5941,7 +6037,7 @@
       </c>
       <c r="K20" s="94"/>
       <c r="L20" s="89">
-        <f>(VLOOKUP(B20,'SKU Details'!D13:AA65,24,0)/1000)*H20</f>
+        <f>+P20</f>
         <v>0</v>
       </c>
     </row>
@@ -5978,34 +6074,47 @@
       </c>
       <c r="K21" s="94"/>
       <c r="L21" s="89">
-        <f>(VLOOKUP(B21,'SKU Details'!D14:AA66,24,0)/1000)*H21</f>
+        <f>+P21</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="114"/>
-      <c r="B22" s="112"/>
+      <c r="B22" s="112" t="s">
+        <v>64</v>
+      </c>
       <c r="C22" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="84">
-        <v>40</v>
+      <c r="D22" s="12">
+        <f>VLOOKUP($B22,'SKU Details'!D15:Y67,3,0)</f>
+        <v>70</v>
+      </c>
+      <c r="E22" s="12">
+        <f>VLOOKUP($B22,'SKU Details'!D15:Y67,4,0)</f>
+        <v>48</v>
       </c>
       <c r="F22" s="12">
-        <v>170</v>
-      </c>
-      <c r="G22" s="102" t="e">
+        <f>VLOOKUP($B22,'SKU Details'!D15:Y67,6,0)</f>
+        <v>190</v>
+      </c>
+      <c r="G22" s="102">
         <f>VLOOKUP($B22,'SKU Details'!D15:Y67,17,0)</f>
-        <v>#N/A</v>
+        <v>1851.4250999999999</v>
       </c>
       <c r="H22" s="18">
-        <v>250</v>
+        <v>654</v>
       </c>
       <c r="I22" s="85"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="16">
+        <f t="shared" si="0"/>
+        <v>1210832.0153999999</v>
+      </c>
       <c r="K22" s="95"/>
-      <c r="L22" s="90"/>
+      <c r="L22" s="89">
+        <f>+P22</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.5">
       <c r="C23" s="2"/>
@@ -6057,13 +6166,8 @@
     <mergeCell ref="C6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="A13:A22">
-    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:B22 H22">
-    <cfRule type="cellIs" dxfId="15" priority="6" stopIfTrue="1" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3">
     <cfRule type="cellIs" dxfId="14" priority="22" stopIfTrue="1" operator="lessThan">
@@ -6079,12 +6183,12 @@
     <cfRule type="duplicateValues" dxfId="12" priority="25"/>
     <cfRule type="duplicateValues" dxfId="11" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H21">
-    <cfRule type="cellIs" dxfId="10" priority="18" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="H12:H22 A13:B22">
+    <cfRule type="cellIs" dxfId="10" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L13:L21">
+  <conditionalFormatting sqref="L13:L22">
     <cfRule type="cellIs" dxfId="9" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
@@ -6125,15 +6229,15 @@
   <sheetData>
     <row r="1" spans="1:17" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="1:17" ht="46.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="150"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="160"/>
       <c r="J2" s="122" t="s">
         <v>6</v>
       </c>
@@ -6143,17 +6247,17 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B3" s="151"/>
-      <c r="C3" s="166" t="s">
+      <c r="B3" s="161"/>
+      <c r="C3" s="176" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="154" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="164" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="155"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="157"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="167"/>
       <c r="J3" s="123" t="s">
         <v>5</v>
       </c>
@@ -6163,15 +6267,15 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B4" s="152"/>
-      <c r="C4" s="168" t="s">
+      <c r="B4" s="162"/>
+      <c r="C4" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="169"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="161"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="170"/>
+      <c r="H4" s="171"/>
       <c r="J4" s="123" t="s">
         <v>54</v>
       </c>
@@ -6181,15 +6285,15 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B5" s="152"/>
-      <c r="C5" s="168" t="s">
+      <c r="B5" s="162"/>
+      <c r="C5" s="178" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="169"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="159"/>
-      <c r="G5" s="160"/>
-      <c r="H5" s="161"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="171"/>
       <c r="J5" s="123" t="s">
         <v>4</v>
       </c>
@@ -6199,15 +6303,15 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="153"/>
-      <c r="C6" s="170" t="s">
+      <c r="B6" s="163"/>
+      <c r="C6" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="171"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="163"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="165"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="175"/>
       <c r="J6" s="123" t="s">
         <v>55</v>
       </c>

--- a/OCT_2026/Reports/Purchase order Distributor.xlsx
+++ b/OCT_2026/Reports/Purchase order Distributor.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB25B76-4F42-4EC1-AF23-0D9BE8C540C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAC18C4-25CA-4101-9D4E-7B66F7A88480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SKU Details" sheetId="16" state="hidden" r:id="rId1"/>
+    <sheet name="SKU Details" sheetId="16" r:id="rId1"/>
     <sheet name="PO" sheetId="21" r:id="rId2"/>
     <sheet name="PO " sheetId="25" r:id="rId3"/>
   </sheets>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SKU Details'!$A$2:$J$145</definedName>
     <definedName name="Z_C0439D6B_0A53_400D_9380_18C16C3AB4D8_.wvu.FilterData" localSheetId="0" hidden="1">'SKU Details'!$A$2:$J$145</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="autoNoTable"/>
   <customWorkbookViews>
     <customWorkbookView name="Farhan Zainul Abedin - Personal View" guid="{C0439D6B-0A53-400D-9380-18C16C3AB4D8}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="803" activeSheetId="18"/>
   </customWorkbookViews>
@@ -1918,6 +1918,7 @@
     <xf numFmtId="167" fontId="39" fillId="21" borderId="1" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2050,7 +2051,6 @@
     <xf numFmtId="3" fontId="18" fillId="3" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="115">
     <cellStyle name="Comma" xfId="17" builtinId="3"/>
@@ -2709,9 +2709,9 @@
     <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.81640625" style="21" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.36328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -2734,97 +2734,97 @@
       </c>
     </row>
     <row r="3" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="142"/>
-      <c r="B3" s="142"/>
-      <c r="C3" s="142"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="142"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="143"/>
-      <c r="Q3" s="143"/>
-      <c r="R3" s="143"/>
-      <c r="S3" s="143"/>
-      <c r="T3" s="143"/>
-      <c r="U3" s="143"/>
-      <c r="V3" s="143"/>
-      <c r="W3" s="143"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="143"/>
+      <c r="A3" s="143"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="144"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="144"/>
+      <c r="Q3" s="144"/>
+      <c r="R3" s="144"/>
+      <c r="S3" s="144"/>
+      <c r="T3" s="144"/>
+      <c r="U3" s="144"/>
+      <c r="V3" s="144"/>
+      <c r="W3" s="144"/>
+      <c r="X3" s="144"/>
+      <c r="Y3" s="144"/>
     </row>
     <row r="4" spans="1:29" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="145" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="120" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="120"/>
-      <c r="D4" s="156" t="s">
+      <c r="D4" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="146" t="s">
+      <c r="E4" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="148" t="s">
+      <c r="F4" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="148"/>
-      <c r="H4" s="149" t="s">
+      <c r="G4" s="149"/>
+      <c r="H4" s="150" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="149"/>
-      <c r="J4" s="150" t="s">
+      <c r="I4" s="150"/>
+      <c r="J4" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="151"/>
-      <c r="L4" s="150" t="s">
+      <c r="K4" s="152"/>
+      <c r="L4" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="151"/>
-      <c r="N4" s="152" t="s">
+      <c r="M4" s="152"/>
+      <c r="N4" s="153" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="152"/>
-      <c r="P4" s="150" t="s">
+      <c r="O4" s="153"/>
+      <c r="P4" s="151" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="151"/>
-      <c r="R4" s="150" t="s">
+      <c r="Q4" s="152"/>
+      <c r="R4" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="S4" s="151"/>
-      <c r="T4" s="153" t="s">
+      <c r="S4" s="152"/>
+      <c r="T4" s="154" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="153"/>
-      <c r="V4" s="154" t="s">
+      <c r="U4" s="154"/>
+      <c r="V4" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="W4" s="155"/>
-      <c r="X4" s="154" t="s">
+      <c r="W4" s="156"/>
+      <c r="X4" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="Y4" s="155"/>
+      <c r="Y4" s="156"/>
     </row>
     <row r="5" spans="1:29" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="145"/>
+      <c r="A5" s="146"/>
       <c r="B5" s="108" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="108" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="157"/>
-      <c r="E5" s="147"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="148"/>
       <c r="F5" s="23" t="s">
         <v>18</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="35">
-        <f t="shared" ref="H14" si="28">I14*G14</f>
+        <f t="shared" ref="H14:H15" si="28">I14*G14</f>
         <v>2000</v>
       </c>
       <c r="I14" s="36">
@@ -3716,10 +3716,11 @@
         <v>70</v>
       </c>
       <c r="G15" s="135">
-        <v>48</v>
-      </c>
-      <c r="H15" s="135">
-        <v>2400</v>
+        <v>12</v>
+      </c>
+      <c r="H15" s="35">
+        <f t="shared" si="28"/>
+        <v>2280</v>
       </c>
       <c r="I15" s="136">
         <v>190</v>
@@ -3730,21 +3731,21 @@
       </c>
       <c r="K15" s="136">
         <f t="shared" si="16"/>
-        <v>58.095129166666666</v>
+        <v>232.38051666666667</v>
       </c>
       <c r="L15" s="137">
         <v>2285.71</v>
       </c>
       <c r="M15" s="137">
         <f t="shared" si="5"/>
-        <v>47.618958333333332</v>
+        <v>190.47583333333333</v>
       </c>
       <c r="N15" s="138">
         <v>0.19</v>
       </c>
       <c r="O15" s="139">
         <f>N15*M15</f>
-        <v>9.0476020833333326</v>
+        <v>36.19040833333333</v>
       </c>
       <c r="P15" s="140"/>
       <c r="Q15" s="139">
@@ -3762,7 +3763,7 @@
       </c>
       <c r="U15" s="137">
         <f t="shared" ref="U15" si="41">M15-O15-Q15-S15</f>
-        <v>38.571356250000001</v>
+        <v>154.285425</v>
       </c>
       <c r="V15" s="137">
         <f t="shared" ref="V15" si="42">T15*$V$2</f>
@@ -3770,7 +3771,7 @@
       </c>
       <c r="W15" s="137">
         <f t="shared" ref="W15" si="43">U15*$V$2</f>
-        <v>6.9428441249999997</v>
+        <v>27.771376499999999</v>
       </c>
       <c r="X15" s="137">
         <f t="shared" ref="X15" si="44">T15+V15</f>
@@ -3778,11 +3779,11 @@
       </c>
       <c r="Y15" s="137">
         <f t="shared" ref="Y15" si="45">U15+W15</f>
-        <v>45.514200375000001</v>
+        <v>182.05680150000001</v>
       </c>
       <c r="AA15" s="66">
         <f t="shared" si="2"/>
-        <v>3.36</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="16" spans="1:29" s="70" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -5449,7 +5450,7 @@
       <selection activeCell="E8" sqref="E8"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-      <autoFilter ref="A2:H123" xr:uid="{0DB22CB4-1492-4A33-9B20-2457272F2CCB}"/>
+      <autoFilter ref="A2:H123" xr:uid="{302DC032-C833-44EE-952C-16F974A7FE3B}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="15">
@@ -5532,15 +5533,15 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="1:16" ht="46.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="159" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="161"/>
       <c r="J2" s="122" t="s">
         <v>6</v>
       </c>
@@ -5550,17 +5551,17 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B3" s="161"/>
-      <c r="C3" s="176" t="s">
+      <c r="B3" s="162"/>
+      <c r="C3" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="165" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="165"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="167"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="168"/>
       <c r="J3" s="123" t="s">
         <v>5</v>
       </c>
@@ -5570,18 +5571,18 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B4" s="162"/>
-      <c r="C4" s="178" t="s">
+      <c r="B4" s="163"/>
+      <c r="C4" s="179" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="179"/>
-      <c r="E4" s="168">
+      <c r="D4" s="180"/>
+      <c r="E4" s="169">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="F4" s="169"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="171"/>
+        <v>46324</v>
+      </c>
+      <c r="F4" s="170"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="172"/>
       <c r="J4" s="123" t="s">
         <v>54</v>
       </c>
@@ -5589,21 +5590,21 @@
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-      <c r="P4" s="182"/>
+      <c r="P4" s="142"/>
     </row>
     <row r="5" spans="1:16" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B5" s="162"/>
-      <c r="C5" s="178" t="s">
+      <c r="B5" s="163"/>
+      <c r="C5" s="179" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="179"/>
-      <c r="E5" s="168">
+      <c r="D5" s="180"/>
+      <c r="E5" s="169">
         <f ca="1">+E4+1</f>
-        <v>46323</v>
-      </c>
-      <c r="F5" s="169"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="171"/>
+        <v>46325</v>
+      </c>
+      <c r="F5" s="170"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="172"/>
       <c r="J5" s="123" t="s">
         <v>4</v>
       </c>
@@ -5613,17 +5614,17 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="163"/>
-      <c r="C6" s="180" t="s">
+      <c r="B6" s="164"/>
+      <c r="C6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="181"/>
-      <c r="E6" s="172" t="s">
+      <c r="D6" s="182"/>
+      <c r="E6" s="173" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="173"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="175"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="175"/>
+      <c r="H6" s="176"/>
       <c r="J6" s="123" t="s">
         <v>55</v>
       </c>
@@ -6092,7 +6093,7 @@
       </c>
       <c r="E22" s="12">
         <f>VLOOKUP($B22,'SKU Details'!D15:Y67,4,0)</f>
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F22" s="12">
         <f>VLOOKUP($B22,'SKU Details'!D15:Y67,6,0)</f>
@@ -6229,15 +6230,15 @@
   <sheetData>
     <row r="1" spans="1:17" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="1:17" ht="46.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="159" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="161"/>
       <c r="J2" s="122" t="s">
         <v>6</v>
       </c>
@@ -6247,17 +6248,17 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B3" s="161"/>
-      <c r="C3" s="176" t="s">
+      <c r="B3" s="162"/>
+      <c r="C3" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="165" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="165"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="167"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="168"/>
       <c r="J3" s="123" t="s">
         <v>5</v>
       </c>
@@ -6267,15 +6268,15 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B4" s="162"/>
-      <c r="C4" s="178" t="s">
+      <c r="B4" s="163"/>
+      <c r="C4" s="179" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="179"/>
-      <c r="E4" s="168"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="171"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="170"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="172"/>
       <c r="J4" s="123" t="s">
         <v>54</v>
       </c>
@@ -6285,15 +6286,15 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
-      <c r="B5" s="162"/>
-      <c r="C5" s="178" t="s">
+      <c r="B5" s="163"/>
+      <c r="C5" s="179" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="179"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="171"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="172"/>
       <c r="J5" s="123" t="s">
         <v>4</v>
       </c>
@@ -6303,15 +6304,15 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="163"/>
-      <c r="C6" s="180" t="s">
+      <c r="B6" s="164"/>
+      <c r="C6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="181"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="175"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="175"/>
+      <c r="H6" s="176"/>
       <c r="J6" s="123" t="s">
         <v>55</v>
       </c>
